--- a/Image_Actions.xlsx
+++ b/Image_Actions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/eb0a5f6c6df775a3/BRNC/Tutor/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/eb0a5f6c6df775a3/BRNC/Tutor/Emergencies/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="316" documentId="8_{261FA775-EA29-4F94-9E5C-BA1B05CB99EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A77F2B40-EB59-4910-8281-B4210ED9FB2F}"/>
+  <xr:revisionPtr revIDLastSave="388" documentId="8_{261FA775-EA29-4F94-9E5C-BA1B05CB99EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0CF4DE27-A0AC-4CC2-A056-7162CD134249}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A628D6DD-06E7-4CAA-8270-1726C440E61F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A628D6DD-06E7-4CAA-8270-1726C440E61F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="233">
   <si>
     <t>x-coord</t>
   </si>
@@ -53,15 +53,6 @@
     <t>Action OFF</t>
   </si>
   <si>
-    <t>Action RIGHT</t>
-  </si>
-  <si>
-    <t>Action LEFT</t>
-  </si>
-  <si>
-    <t>ACTION BOTH</t>
-  </si>
-  <si>
     <t>Fuel Cock</t>
   </si>
   <si>
@@ -137,12 +128,6 @@
     <t>AUX fuel pump</t>
   </si>
   <si>
-    <t>AUX fuel pump ON</t>
-  </si>
-  <si>
-    <t>AUX fuel pump OFF</t>
-  </si>
-  <si>
     <t>TRIM full and free movement</t>
   </si>
   <si>
@@ -308,9 +293,6 @@
     <t>CO DETECTOR</t>
   </si>
   <si>
-    <t>CO DETECTOR NORMAL</t>
-  </si>
-  <si>
     <t>GPS 1</t>
   </si>
   <si>
@@ -440,9 +422,6 @@
     <t>THROTTLE EXERCISE</t>
   </si>
   <si>
-    <t>RPM lever EXERCISE</t>
-  </si>
-  <si>
     <t>RPM lever set HIGH</t>
   </si>
   <si>
@@ -578,9 +557,6 @@
     <t>Mixture lever GATED</t>
   </si>
   <si>
-    <t>Mixture lever UNGATED</t>
-  </si>
-  <si>
     <t>GEN switch ON</t>
   </si>
   <si>
@@ -665,9 +641,6 @@
     <t>Altimeters, QFE set</t>
   </si>
   <si>
-    <t>Fuel imbalance &lt; 20 litres</t>
-  </si>
-  <si>
     <t>COM 1 OFF</t>
   </si>
   <si>
@@ -723,6 +696,45 @@
   </si>
   <si>
     <t>CWP Display: Condition, GEN and LO OIL captions lit</t>
+  </si>
+  <si>
+    <t>RPM Lever As required</t>
+  </si>
+  <si>
+    <t>Mixture lever Ungate</t>
+  </si>
+  <si>
+    <t>Aux FUEL PUMP ON</t>
+  </si>
+  <si>
+    <t>Aux FUEL PUMP OFF</t>
+  </si>
+  <si>
+    <t>FUEL QTY Check Contents</t>
+  </si>
+  <si>
+    <t>START CTRL CB Pull</t>
+  </si>
+  <si>
+    <t>MAIN BUS CB PULL</t>
+  </si>
+  <si>
+    <t>ELT ON</t>
+  </si>
+  <si>
+    <t>Cabin conditioning Cold, screen</t>
+  </si>
+  <si>
+    <t>CO DETECTOR CHECK</t>
+  </si>
+  <si>
+    <t>Canopy Set ventilation position</t>
+  </si>
+  <si>
+    <t>Speed Below 80 kts if possible</t>
+  </si>
+  <si>
+    <t>Air vents Open</t>
   </si>
 </sst>
 </file>
@@ -738,12 +750,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -758,8 +776,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1098,21 +1117,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4F254DD-9EB8-41F6-BF96-40D2BFDFABED}">
-  <dimension ref="A1:K86"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H90"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="46.33203125" customWidth="1"/>
-    <col min="2" max="2" width="20.5546875" customWidth="1"/>
-    <col min="3" max="3" width="20.88671875" customWidth="1"/>
-    <col min="4" max="4" width="31.6640625" customWidth="1"/>
-    <col min="5" max="5" width="33.44140625" customWidth="1"/>
-    <col min="6" max="6" width="38.44140625" customWidth="1"/>
-    <col min="7" max="7" width="14.33203125" customWidth="1"/>
-    <col min="8" max="8" width="12.6640625" customWidth="1"/>
-    <col min="9" max="9" width="12.88671875" customWidth="1"/>
+    <col min="1" max="1" width="46.28515625" customWidth="1"/>
+    <col min="2" max="2" width="20.5703125" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" customWidth="1"/>
+    <col min="4" max="4" width="31.7109375" customWidth="1"/>
+    <col min="5" max="5" width="33.42578125" customWidth="1"/>
+    <col min="6" max="6" width="38.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1129,41 +1145,32 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" t="s">
+      <c r="B2" s="1">
+        <v>433</v>
+      </c>
+      <c r="C2" s="1">
+        <v>588</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2">
-        <v>433</v>
-      </c>
-      <c r="C2">
-        <v>588</v>
-      </c>
-      <c r="D2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E2" t="s">
-        <v>168</v>
-      </c>
-      <c r="F2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>10</v>
       </c>
       <c r="B3">
         <v>395</v>
@@ -1172,38 +1179,38 @@
         <v>486</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E3" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F3" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="1">
         <v>432</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="1">
         <v>479</v>
       </c>
-      <c r="D4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F4" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>464</v>
@@ -1212,18 +1219,18 @@
         <v>483</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F5" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B6">
         <v>440</v>
@@ -1232,18 +1239,18 @@
         <v>451</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E6" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B7">
         <v>409</v>
@@ -1252,138 +1259,138 @@
         <v>439</v>
       </c>
       <c r="D7" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E7" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="1">
+        <v>307</v>
+      </c>
+      <c r="C8" s="1">
+        <v>359</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B9" s="1">
+        <v>311</v>
+      </c>
+      <c r="C9" s="1">
+        <v>374</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="1">
+        <v>311</v>
+      </c>
+      <c r="C10" s="1">
+        <v>389</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="1">
+        <v>311</v>
+      </c>
+      <c r="C11" s="1">
+        <v>404</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B8">
+      <c r="B12" s="1">
+        <v>312</v>
+      </c>
+      <c r="C12" s="1">
+        <v>422</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="1">
         <v>307</v>
       </c>
-      <c r="C8">
-        <v>359</v>
-      </c>
-      <c r="D8" t="s">
-        <v>197</v>
-      </c>
-      <c r="E8" t="s">
-        <v>203</v>
-      </c>
-      <c r="F8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>177</v>
-      </c>
-      <c r="B9">
-        <v>311</v>
-      </c>
-      <c r="C9">
-        <v>374</v>
-      </c>
-      <c r="D9" t="s">
-        <v>198</v>
-      </c>
-      <c r="E9" t="s">
-        <v>203</v>
-      </c>
-      <c r="F9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10">
-        <v>311</v>
-      </c>
-      <c r="C10">
-        <v>389</v>
-      </c>
-      <c r="D10" t="s">
-        <v>199</v>
-      </c>
-      <c r="E10" t="s">
-        <v>203</v>
-      </c>
-      <c r="F10" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11">
-        <v>311</v>
-      </c>
-      <c r="C11">
-        <v>404</v>
-      </c>
-      <c r="D11" t="s">
-        <v>200</v>
-      </c>
-      <c r="E11" t="s">
-        <v>203</v>
-      </c>
-      <c r="F11" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12">
-        <v>312</v>
-      </c>
-      <c r="C12">
-        <v>422</v>
-      </c>
-      <c r="D12" t="s">
-        <v>201</v>
-      </c>
-      <c r="E12" t="s">
-        <v>203</v>
-      </c>
-      <c r="F12" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13">
-        <v>307</v>
-      </c>
-      <c r="C13">
+      <c r="C13" s="1">
         <v>437</v>
       </c>
-      <c r="D13" t="s">
-        <v>202</v>
-      </c>
-      <c r="E13" t="s">
-        <v>203</v>
-      </c>
-      <c r="F13" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D13" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="B14">
         <v>395</v>
@@ -1392,38 +1399,38 @@
         <v>398</v>
       </c>
       <c r="D14" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="E14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="F14" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="1">
         <v>426</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="1">
         <v>381</v>
       </c>
-      <c r="D15" t="s">
-        <v>135</v>
-      </c>
-      <c r="E15" t="s">
-        <v>136</v>
-      </c>
-      <c r="F15" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D15" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B16">
         <v>511</v>
@@ -1432,78 +1439,78 @@
         <v>395</v>
       </c>
       <c r="D16" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" t="s">
+        <v>31</v>
+      </c>
+      <c r="F16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B17" s="1">
+        <v>447</v>
+      </c>
+      <c r="C17" s="1">
+        <v>403</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="1">
+        <v>456</v>
+      </c>
+      <c r="C18" s="1">
+        <v>381</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E16" t="s">
-        <v>36</v>
-      </c>
-      <c r="F16" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>178</v>
-      </c>
-      <c r="B17">
-        <v>447</v>
-      </c>
-      <c r="C17">
-        <v>403</v>
-      </c>
-      <c r="D17" t="s">
-        <v>179</v>
-      </c>
-      <c r="E17" t="s">
-        <v>180</v>
-      </c>
-      <c r="F17" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18">
-        <v>456</v>
-      </c>
-      <c r="C18">
-        <v>381</v>
-      </c>
-      <c r="D18" t="s">
-        <v>38</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="B19" s="1">
+        <v>388</v>
+      </c>
+      <c r="C19" s="1">
+        <v>347</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F18" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19">
-        <v>388</v>
-      </c>
-      <c r="C19">
-        <v>347</v>
-      </c>
-      <c r="D19" t="s">
+      <c r="E19" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>24</v>
-      </c>
-      <c r="E19" t="s">
-        <v>22</v>
-      </c>
-      <c r="F19" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>27</v>
       </c>
       <c r="B20">
         <v>441</v>
@@ -1512,21 +1519,21 @@
         <v>345</v>
       </c>
       <c r="D20" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" t="s">
         <v>25</v>
       </c>
-      <c r="F20" t="s">
-        <v>28</v>
-      </c>
-      <c r="K20" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="H20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="B21">
         <v>415</v>
@@ -1535,158 +1542,158 @@
         <v>350</v>
       </c>
       <c r="D21" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="E21" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F21" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" s="1">
+        <v>597</v>
+      </c>
+      <c r="C22" s="1">
+        <v>316</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" s="1">
+        <v>585</v>
+      </c>
+      <c r="C23" s="1">
+        <v>318</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B22">
-        <v>597</v>
-      </c>
-      <c r="C22">
-        <v>316</v>
-      </c>
-      <c r="D22" t="s">
-        <v>31</v>
-      </c>
-      <c r="E22" t="s">
-        <v>183</v>
-      </c>
-      <c r="F22" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>30</v>
-      </c>
-      <c r="B23">
-        <v>585</v>
-      </c>
-      <c r="C23">
+      <c r="B24" s="1">
+        <v>564</v>
+      </c>
+      <c r="C24" s="1">
         <v>318</v>
       </c>
-      <c r="D23" t="s">
-        <v>181</v>
-      </c>
-      <c r="E23" t="s">
-        <v>182</v>
-      </c>
-      <c r="F23" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>32</v>
-      </c>
-      <c r="B24">
-        <v>564</v>
-      </c>
-      <c r="C24">
-        <v>318</v>
-      </c>
-      <c r="D24" t="s">
-        <v>33</v>
-      </c>
-      <c r="E24" t="s">
-        <v>34</v>
-      </c>
-      <c r="F24" t="s">
+      <c r="D24" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B25" s="1">
+        <v>80</v>
+      </c>
+      <c r="C25" s="1">
+        <v>526</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>176</v>
-      </c>
-      <c r="B25">
-        <v>80</v>
-      </c>
-      <c r="C25">
-        <v>526</v>
-      </c>
-      <c r="D25" t="s">
-        <v>173</v>
-      </c>
-      <c r="E25" t="s">
-        <v>176</v>
-      </c>
-      <c r="F25" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>174</v>
-      </c>
-      <c r="B26">
+      <c r="E25" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B26" s="1">
         <v>108</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="1">
         <v>500</v>
       </c>
-      <c r="D26" t="s">
-        <v>174</v>
-      </c>
-      <c r="E26" t="s">
-        <v>176</v>
-      </c>
-      <c r="F26" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>175</v>
-      </c>
-      <c r="B27">
+      <c r="D26" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B27" s="1">
         <v>139</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="1">
         <v>498</v>
       </c>
-      <c r="D27" t="s">
-        <v>175</v>
-      </c>
-      <c r="E27" t="s">
-        <v>176</v>
-      </c>
-      <c r="F27" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>173</v>
-      </c>
-      <c r="B28">
+      <c r="D27" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B28" s="1">
         <v>177</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="1">
         <v>533</v>
       </c>
-      <c r="D28" t="s">
-        <v>173</v>
-      </c>
-      <c r="E28" t="s">
-        <v>176</v>
-      </c>
-      <c r="F28" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D28" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B29">
         <v>498</v>
@@ -1695,18 +1702,18 @@
         <v>315</v>
       </c>
       <c r="D29" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E29" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F29" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B30">
         <v>482</v>
@@ -1715,18 +1722,18 @@
         <v>316</v>
       </c>
       <c r="D30" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E30" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F30" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B31">
         <v>471</v>
@@ -1735,18 +1742,18 @@
         <v>316</v>
       </c>
       <c r="D31" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E31" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F31" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B32">
         <v>423</v>
@@ -1755,18 +1762,18 @@
         <v>319</v>
       </c>
       <c r="D32" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E32" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F32" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B33">
         <v>401</v>
@@ -1775,18 +1782,18 @@
         <v>319</v>
       </c>
       <c r="D33" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E33" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="F33" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B34">
         <v>547</v>
@@ -1795,18 +1802,18 @@
         <v>318</v>
       </c>
       <c r="D34" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E34" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F34" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B35">
         <v>772</v>
@@ -1815,38 +1822,38 @@
         <v>228</v>
       </c>
       <c r="D35" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E35" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F35" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>59</v>
-      </c>
-      <c r="B36">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B36" s="1">
         <v>725</v>
       </c>
-      <c r="C36">
+      <c r="C36" s="1">
         <v>276</v>
       </c>
-      <c r="D36" t="s">
-        <v>36</v>
-      </c>
-      <c r="E36" t="s">
-        <v>36</v>
-      </c>
-      <c r="F36" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D36" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B37">
         <v>728</v>
@@ -1855,18 +1862,18 @@
         <v>226</v>
       </c>
       <c r="D37" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E37" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F37" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B38">
         <v>661</v>
@@ -1875,18 +1882,18 @@
         <v>153</v>
       </c>
       <c r="D38" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="E38" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="F38" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B39">
         <v>591</v>
@@ -1895,18 +1902,18 @@
         <v>228</v>
       </c>
       <c r="D39" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E39" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F39" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B40">
         <v>731</v>
@@ -1915,18 +1922,18 @@
         <v>156</v>
       </c>
       <c r="D40" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E40" t="s">
+        <v>200</v>
+      </c>
+      <c r="F40" t="s">
         <v>208</v>
       </c>
-      <c r="F40" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B41">
         <v>660</v>
@@ -1935,18 +1942,18 @@
         <v>229</v>
       </c>
       <c r="D41" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="E41" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F41" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>71</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>76</v>
       </c>
       <c r="B42">
         <v>576</v>
@@ -1955,18 +1962,18 @@
         <v>278</v>
       </c>
       <c r="D42" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E42" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F42" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B43">
         <v>606</v>
@@ -1975,18 +1982,18 @@
         <v>276</v>
       </c>
       <c r="D43" t="s">
+        <v>69</v>
+      </c>
+      <c r="E43" t="s">
+        <v>70</v>
+      </c>
+      <c r="F43" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
         <v>74</v>
-      </c>
-      <c r="E43" t="s">
-        <v>75</v>
-      </c>
-      <c r="F43" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>79</v>
       </c>
       <c r="B44">
         <v>659</v>
@@ -1995,18 +2002,18 @@
         <v>283</v>
       </c>
       <c r="D44" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="E44" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F44" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B45">
         <v>643</v>
@@ -2015,18 +2022,18 @@
         <v>322</v>
       </c>
       <c r="D45" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E45" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F45" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B46">
         <v>713</v>
@@ -2035,18 +2042,18 @@
         <v>305</v>
       </c>
       <c r="D46" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E46" t="s">
+        <v>82</v>
+      </c>
+      <c r="F46" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
         <v>87</v>
-      </c>
-      <c r="F46" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>93</v>
       </c>
       <c r="B47">
         <v>365</v>
@@ -2055,18 +2062,18 @@
         <v>128</v>
       </c>
       <c r="D47" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="E47" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F47" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B48">
         <v>590</v>
@@ -2075,38 +2082,38 @@
         <v>274</v>
       </c>
       <c r="D48" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E48" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F48" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>98</v>
-      </c>
-      <c r="B49">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B49" s="1">
         <v>592</v>
       </c>
-      <c r="C49">
+      <c r="C49" s="1">
         <v>156</v>
       </c>
-      <c r="D49" t="s">
-        <v>36</v>
-      </c>
-      <c r="E49" t="s">
-        <v>36</v>
-      </c>
-      <c r="F49" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D49" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="B50">
         <v>524</v>
@@ -2115,18 +2122,18 @@
         <v>130</v>
       </c>
       <c r="D50" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E50" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F50" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="B51">
         <v>174</v>
@@ -2135,18 +2142,18 @@
         <v>227</v>
       </c>
       <c r="D51" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E51" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F51" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B52">
         <v>508</v>
@@ -2155,18 +2162,18 @@
         <v>274</v>
       </c>
       <c r="D52" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="E52" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="F52" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B53">
         <v>367</v>
@@ -2175,18 +2182,18 @@
         <v>206</v>
       </c>
       <c r="D53" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E53" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="F53" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="B54">
         <v>398</v>
@@ -2195,18 +2202,18 @@
         <v>87</v>
       </c>
       <c r="D54" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="E54" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="F54" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="B55">
         <v>422</v>
@@ -2215,18 +2222,18 @@
         <v>82</v>
       </c>
       <c r="D55" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="E55" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="F55" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="B56">
         <v>414</v>
@@ -2235,18 +2242,18 @@
         <v>50</v>
       </c>
       <c r="D56" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E56" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F56" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
         <v>109</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>115</v>
       </c>
       <c r="B57">
         <v>759</v>
@@ -2255,38 +2262,38 @@
         <v>557</v>
       </c>
       <c r="D57" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="E57" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F57" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>113</v>
-      </c>
-      <c r="B58">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B58" s="1">
         <v>808</v>
       </c>
-      <c r="C58">
+      <c r="C58" s="1">
         <v>467</v>
       </c>
-      <c r="D58" t="s">
-        <v>114</v>
-      </c>
-      <c r="E58" t="s">
-        <v>36</v>
-      </c>
-      <c r="F58" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D58" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="B59">
         <v>523</v>
@@ -2295,18 +2302,18 @@
         <v>189</v>
       </c>
       <c r="D59" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E59" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F59" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B60">
         <v>417</v>
@@ -2315,38 +2322,38 @@
         <v>278</v>
       </c>
       <c r="D60" t="s">
-        <v>221</v>
+        <v>31</v>
       </c>
       <c r="E60" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F60" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>89</v>
-      </c>
-      <c r="B61">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B61" s="1">
         <v>417</v>
       </c>
-      <c r="C61">
+      <c r="C61" s="1">
         <v>242</v>
       </c>
-      <c r="D61" t="s">
-        <v>36</v>
-      </c>
-      <c r="E61" t="s">
-        <v>36</v>
-      </c>
-      <c r="F61" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D61" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="B62">
         <v>240</v>
@@ -2355,18 +2362,18 @@
         <v>158</v>
       </c>
       <c r="D62" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E62" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F62" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="B63">
         <v>310</v>
@@ -2375,18 +2382,18 @@
         <v>156</v>
       </c>
       <c r="D63" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E63" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F63" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="B64">
         <v>110</v>
@@ -2395,18 +2402,18 @@
         <v>158</v>
       </c>
       <c r="D64" t="s">
-        <v>221</v>
+        <v>31</v>
       </c>
       <c r="E64" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F64" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="B65">
         <v>106</v>
@@ -2415,18 +2422,18 @@
         <v>217</v>
       </c>
       <c r="D65" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="E65" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F65" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="B66">
         <v>121</v>
@@ -2435,38 +2442,38 @@
         <v>262</v>
       </c>
       <c r="D66" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="E66" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F66" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
-        <v>122</v>
-      </c>
-      <c r="B67">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B67" s="1">
         <v>147</v>
       </c>
-      <c r="C67">
+      <c r="C67" s="1">
         <v>312</v>
       </c>
-      <c r="D67" t="s">
-        <v>36</v>
-      </c>
-      <c r="E67" t="s">
-        <v>36</v>
-      </c>
-      <c r="F67" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D67" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="B68">
         <v>246</v>
@@ -2475,18 +2482,18 @@
         <v>318</v>
       </c>
       <c r="D68" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="E68" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F68" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="B69">
         <v>305</v>
@@ -2495,18 +2502,18 @@
         <v>316</v>
       </c>
       <c r="D69" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E69" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="F69" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B70">
         <v>349</v>
@@ -2515,18 +2522,18 @@
         <v>314</v>
       </c>
       <c r="D70" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E70" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F70" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="B71">
         <v>726</v>
@@ -2535,18 +2542,18 @@
         <v>472</v>
       </c>
       <c r="D71" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="E71" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F71" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="B72">
         <v>666</v>
@@ -2555,18 +2562,18 @@
         <v>555</v>
       </c>
       <c r="D72" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="E72" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F72" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="B73">
         <v>795</v>
@@ -2575,18 +2582,18 @@
         <v>554</v>
       </c>
       <c r="D73" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="E73" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F73" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="B74">
         <v>444</v>
@@ -2595,38 +2602,38 @@
         <v>205</v>
       </c>
       <c r="D74" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E74" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="F74" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
-        <v>150</v>
-      </c>
-      <c r="B75">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B75" s="1">
         <v>417</v>
       </c>
-      <c r="C75">
+      <c r="C75" s="1">
         <v>6</v>
       </c>
-      <c r="D75" t="s">
-        <v>36</v>
-      </c>
-      <c r="E75" t="s">
-        <v>151</v>
-      </c>
-      <c r="F75" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D75" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="B76">
         <v>699</v>
@@ -2635,18 +2642,18 @@
         <v>559</v>
       </c>
       <c r="D76" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E76" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F76" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B77">
         <v>681</v>
@@ -2655,18 +2662,18 @@
         <v>178</v>
       </c>
       <c r="D77" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E77" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F77" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="B78">
         <v>442</v>
@@ -2675,18 +2682,18 @@
         <v>153</v>
       </c>
       <c r="D78" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="E78" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="F78" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="B79">
         <v>286</v>
@@ -2695,38 +2702,38 @@
         <v>230</v>
       </c>
       <c r="D79" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E79" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F79" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
-        <v>186</v>
-      </c>
-      <c r="B80">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B80" s="1">
         <v>172</v>
       </c>
-      <c r="C80">
+      <c r="C80" s="1">
         <v>151</v>
       </c>
-      <c r="D80" t="s">
-        <v>36</v>
-      </c>
-      <c r="E80" t="s">
-        <v>36</v>
-      </c>
-      <c r="F80" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D80" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="B81">
         <v>244</v>
@@ -2735,18 +2742,18 @@
         <v>278</v>
       </c>
       <c r="D81" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="E81" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F81" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="B82">
         <v>381</v>
@@ -2755,18 +2762,18 @@
         <v>156</v>
       </c>
       <c r="D82" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="E82" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="F82" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B83">
         <v>642</v>
@@ -2775,18 +2782,18 @@
         <v>431</v>
       </c>
       <c r="D83" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="E83" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F83" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="B84">
         <v>522</v>
@@ -2795,18 +2802,18 @@
         <v>316</v>
       </c>
       <c r="D84" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="E84" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="F84" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="B85">
         <v>460</v>
@@ -2815,18 +2822,18 @@
         <v>88</v>
       </c>
       <c r="D85" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E85" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F85" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="B86">
         <v>376</v>
@@ -2835,13 +2842,93 @@
         <v>88</v>
       </c>
       <c r="D86" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="E86" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F86" t="s">
-        <v>36</v>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B87" s="1">
+        <v>114</v>
+      </c>
+      <c r="C87" s="1">
+        <v>133</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B88" s="1">
+        <v>404</v>
+      </c>
+      <c r="C88" s="1">
+        <v>280</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B89" s="1">
+        <v>806</v>
+      </c>
+      <c r="C89" s="1">
+        <v>314</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B90" s="1">
+        <v>57</v>
+      </c>
+      <c r="C90" s="1">
+        <v>252</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/Image_Actions.xlsx
+++ b/Image_Actions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/eb0a5f6c6df775a3/BRNC/Tutor/Emergencies/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="388" documentId="8_{261FA775-EA29-4F94-9E5C-BA1B05CB99EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0CF4DE27-A0AC-4CC2-A056-7162CD134249}"/>
+  <xr:revisionPtr revIDLastSave="401" documentId="8_{261FA775-EA29-4F94-9E5C-BA1B05CB99EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{809CF96B-53DA-4C61-8F5B-A9B2A252C494}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A628D6DD-06E7-4CAA-8270-1726C440E61F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A628D6DD-06E7-4CAA-8270-1726C440E61F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="236">
   <si>
     <t>x-coord</t>
   </si>
@@ -735,6 +735,15 @@
   </si>
   <si>
     <t>Air vents Open</t>
+  </si>
+  <si>
+    <t>THROTTLE Set approx 20'' MP</t>
+  </si>
+  <si>
+    <t>MP</t>
+  </si>
+  <si>
+    <t>IAS Minimise changes</t>
   </si>
 </sst>
 </file>
@@ -794,10 +803,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1117,18 +1122,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4F254DD-9EB8-41F6-BF96-40D2BFDFABED}">
-  <dimension ref="A1:H90"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H91"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="46.28515625" customWidth="1"/>
-    <col min="2" max="2" width="20.5703125" customWidth="1"/>
-    <col min="3" max="3" width="20.85546875" customWidth="1"/>
-    <col min="4" max="4" width="31.7109375" customWidth="1"/>
-    <col min="5" max="5" width="33.42578125" customWidth="1"/>
-    <col min="6" max="6" width="38.42578125" customWidth="1"/>
+    <col min="1" max="1" width="46.33203125" customWidth="1"/>
+    <col min="2" max="2" width="20.5546875" customWidth="1"/>
+    <col min="3" max="3" width="20.88671875" customWidth="1"/>
+    <col min="4" max="4" width="31.6640625" customWidth="1"/>
+    <col min="5" max="5" width="33.44140625" customWidth="1"/>
+    <col min="6" max="6" width="38.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1148,7 +1153,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -1168,7 +1173,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1188,7 +1193,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="4" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -1208,7 +1213,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1228,7 +1233,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1248,7 +1253,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -1268,7 +1273,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
@@ -1288,7 +1293,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>170</v>
       </c>
@@ -1308,7 +1313,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>12</v>
       </c>
@@ -1328,7 +1333,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>13</v>
       </c>
@@ -1348,7 +1353,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>14</v>
       </c>
@@ -1368,7 +1373,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>15</v>
       </c>
@@ -1388,7 +1393,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>126</v>
       </c>
@@ -1408,7 +1413,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>16</v>
       </c>
@@ -1428,7 +1433,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -1448,7 +1453,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>171</v>
       </c>
@@ -1468,7 +1473,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>32</v>
       </c>
@@ -1488,7 +1493,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="19" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>20</v>
       </c>
@@ -1508,7 +1513,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -1531,7 +1536,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>142</v>
       </c>
@@ -1551,7 +1556,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="22" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>26</v>
       </c>
@@ -1571,7 +1576,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>27</v>
       </c>
@@ -1591,7 +1596,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>29</v>
       </c>
@@ -1611,7 +1616,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="25" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>169</v>
       </c>
@@ -1631,7 +1636,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>167</v>
       </c>
@@ -1651,7 +1656,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>168</v>
       </c>
@@ -1671,7 +1676,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>166</v>
       </c>
@@ -1691,7 +1696,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>35</v>
       </c>
@@ -1711,7 +1716,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>37</v>
       </c>
@@ -1731,7 +1736,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>40</v>
       </c>
@@ -1751,7 +1756,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>44</v>
       </c>
@@ -1771,7 +1776,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>46</v>
       </c>
@@ -1791,7 +1796,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>49</v>
       </c>
@@ -1811,7 +1816,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>52</v>
       </c>
@@ -1831,7 +1836,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="36" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>54</v>
       </c>
@@ -1851,7 +1856,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>56</v>
       </c>
@@ -1871,7 +1876,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>58</v>
       </c>
@@ -1891,7 +1896,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>79</v>
       </c>
@@ -1911,7 +1916,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>62</v>
       </c>
@@ -1931,7 +1936,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>65</v>
       </c>
@@ -1951,7 +1956,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>71</v>
       </c>
@@ -1971,7 +1976,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>68</v>
       </c>
@@ -1991,7 +1996,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>74</v>
       </c>
@@ -2011,7 +2016,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>77</v>
       </c>
@@ -2031,7 +2036,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>80</v>
       </c>
@@ -2051,7 +2056,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>87</v>
       </c>
@@ -2071,7 +2076,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>89</v>
       </c>
@@ -2091,7 +2096,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="49" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>92</v>
       </c>
@@ -2105,33 +2110,33 @@
         <v>231</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>31</v>
+        <v>235</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+    <row r="50" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="B50">
+      <c r="B50" s="1">
         <v>524</v>
       </c>
-      <c r="C50">
+      <c r="C50" s="1">
         <v>130</v>
       </c>
-      <c r="D50" t="s">
-        <v>31</v>
-      </c>
-      <c r="E50" t="s">
-        <v>31</v>
-      </c>
-      <c r="F50" t="s">
+      <c r="D50" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F50" s="1" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>110</v>
       </c>
@@ -2151,7 +2156,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>96</v>
       </c>
@@ -2171,7 +2176,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>85</v>
       </c>
@@ -2191,7 +2196,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>101</v>
       </c>
@@ -2211,7 +2216,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>206</v>
       </c>
@@ -2231,7 +2236,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>102</v>
       </c>
@@ -2251,7 +2256,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>109</v>
       </c>
@@ -2271,7 +2276,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="58" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>107</v>
       </c>
@@ -2291,7 +2296,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>94</v>
       </c>
@@ -2311,7 +2316,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>99</v>
       </c>
@@ -2331,7 +2336,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="61" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>84</v>
       </c>
@@ -2351,7 +2356,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>105</v>
       </c>
@@ -2371,7 +2376,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>104</v>
       </c>
@@ -2391,7 +2396,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>113</v>
       </c>
@@ -2411,7 +2416,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>114</v>
       </c>
@@ -2431,7 +2436,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>115</v>
       </c>
@@ -2451,7 +2456,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="67" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>116</v>
       </c>
@@ -2471,7 +2476,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>185</v>
       </c>
@@ -2491,7 +2496,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>122</v>
       </c>
@@ -2511,7 +2516,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>124</v>
       </c>
@@ -2531,7 +2536,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>132</v>
       </c>
@@ -2551,7 +2556,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>135</v>
       </c>
@@ -2571,7 +2576,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>137</v>
       </c>
@@ -2591,7 +2596,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>139</v>
       </c>
@@ -2611,7 +2616,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="75" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>143</v>
       </c>
@@ -2631,7 +2636,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>146</v>
       </c>
@@ -2651,7 +2656,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>64</v>
       </c>
@@ -2671,7 +2676,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>152</v>
       </c>
@@ -2691,7 +2696,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>177</v>
       </c>
@@ -2711,7 +2716,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="80" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>178</v>
       </c>
@@ -2725,13 +2730,13 @@
         <v>231</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>31</v>
+        <v>235</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>179</v>
       </c>
@@ -2751,7 +2756,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>180</v>
       </c>
@@ -2771,7 +2776,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>196</v>
       </c>
@@ -2791,7 +2796,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>203</v>
       </c>
@@ -2811,7 +2816,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>215</v>
       </c>
@@ -2831,7 +2836,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>217</v>
       </c>
@@ -2851,7 +2856,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="87" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
         <v>225</v>
       </c>
@@ -2865,13 +2870,13 @@
         <v>225</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>31</v>
+        <v>225</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="88" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
         <v>226</v>
       </c>
@@ -2885,13 +2890,13 @@
         <v>226</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>31</v>
+        <v>226</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="89" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
         <v>232</v>
       </c>
@@ -2911,7 +2916,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
         <v>232</v>
       </c>
@@ -2928,6 +2933,26 @@
         <v>31</v>
       </c>
       <c r="F90" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A91" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B91" s="1">
+        <v>642</v>
+      </c>
+      <c r="C91" s="1">
+        <v>460</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F91" s="1" t="s">
         <v>31</v>
       </c>
     </row>
